--- a/data/mini-example-resilience/Power_ThermalGen.xlsx
+++ b/data/mini-example-resilience/Power_ThermalGen.xlsx
@@ -8,14 +8,27 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Simon Malacek\Code\LEGO-Pyomo\data\mini-example-resilience\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6683C113-D65C-4B57-9961-50DE40D73A94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45E20966-77DC-4EF7-8755-4DB15653083A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ScenarioA" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -410,10 +423,10 @@
     <t>Node_1</t>
   </si>
   <si>
-    <t>Gas</t>
-  </si>
-  <si>
-    <t>Diesel</t>
+    <t>BackupGenerator</t>
+  </si>
+  <si>
+    <t>BackupGen</t>
   </si>
 </sst>
 </file>
@@ -1415,16 +1428,16 @@
         <v>0</v>
       </c>
       <c r="G8" s="14">
-        <v>500</v>
+        <v>1</v>
       </c>
       <c r="H8" s="14">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I8" s="14">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="J8" s="14">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="K8" s="13">
         <v>1</v>
@@ -1433,28 +1446,28 @@
         <v>1</v>
       </c>
       <c r="M8" s="14">
-        <v>200</v>
+        <v>2</v>
       </c>
       <c r="N8" s="14">
-        <v>-200</v>
+        <v>-2</v>
       </c>
       <c r="O8" s="14">
         <v>4</v>
       </c>
       <c r="P8" s="15">
-        <v>32.68</v>
+        <v>200</v>
       </c>
       <c r="Q8" s="15">
-        <v>0.4777777777777778</v>
+        <v>0.35</v>
       </c>
       <c r="R8" s="15">
-        <v>348.83720930232562</v>
+        <v>0.01</v>
       </c>
       <c r="S8" s="15">
         <v>4</v>
       </c>
       <c r="T8" s="15">
-        <v>1162.7906976744191</v>
+        <v>0.01</v>
       </c>
       <c r="U8" s="15"/>
       <c r="V8" s="13">
